--- a/Excel/temp.xlsx
+++ b/Excel/temp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F551EBF3-341A-469F-84A3-E733FA9AECE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1643D7B0-4455-4274-9B81-66FEC8075FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="BB1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -126,7 +126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BP1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="BR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -148,7 +148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="CT1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="423">
   <si>
     <t>Id</t>
   </si>
@@ -1535,13 +1535,33 @@
   </si>
   <si>
     <t>BackSkelPath</t>
+  </si>
+  <si>
+    <t>优先Buff</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义优先级</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderBuff</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderExpression</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1606,6 +1626,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1644,7 +1680,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1673,6 +1709,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5364,7 +5406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH741"/>
+  <dimension ref="A1:DJ741"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -5404,49 +5446,49 @@
     <col min="38" max="39" width="8.33203125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
     <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="43" width="11.83203125" customWidth="1"/>
-    <col min="44" max="44" width="18.4140625" customWidth="1"/>
-    <col min="45" max="45" width="12.25" customWidth="1"/>
-    <col min="46" max="46" width="11.9140625" customWidth="1"/>
-    <col min="47" max="47" width="19.58203125" customWidth="1"/>
-    <col min="48" max="48" width="12.6640625" customWidth="1"/>
-    <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="51" width="11.75" customWidth="1"/>
-    <col min="52" max="52" width="19.75" customWidth="1"/>
-    <col min="53" max="53" width="5.08203125" customWidth="1"/>
-    <col min="54" max="54" width="8.5" customWidth="1"/>
-    <col min="55" max="55" width="13.5" customWidth="1"/>
-    <col min="56" max="56" width="14.6640625" customWidth="1"/>
-    <col min="57" max="57" width="10.1640625" customWidth="1"/>
-    <col min="58" max="58" width="8.25" customWidth="1"/>
-    <col min="59" max="65" width="8.33203125" customWidth="1"/>
-    <col min="66" max="68" width="11.25" customWidth="1"/>
-    <col min="69" max="69" width="6.58203125" customWidth="1"/>
-    <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.33203125" style="4" customWidth="1"/>
-    <col min="73" max="74" width="8.5" style="4" customWidth="1"/>
-    <col min="75" max="76" width="7.83203125" style="4" customWidth="1"/>
-    <col min="77" max="77" width="22.1640625" style="4" customWidth="1"/>
-    <col min="78" max="78" width="13.5" customWidth="1"/>
-    <col min="79" max="79" width="21.1640625" customWidth="1"/>
-    <col min="80" max="80" width="15.75" customWidth="1"/>
-    <col min="81" max="81" width="15.58203125" customWidth="1"/>
-    <col min="82" max="82" width="12.83203125" customWidth="1"/>
-    <col min="83" max="83" width="16.1640625" customWidth="1"/>
-    <col min="85" max="85" width="16" customWidth="1"/>
-    <col min="86" max="87" width="12.83203125" customWidth="1"/>
-    <col min="88" max="88" width="23.58203125" customWidth="1"/>
-    <col min="89" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="17.08203125" customWidth="1"/>
-    <col min="97" max="97" width="14" customWidth="1"/>
-    <col min="98" max="98" width="8" customWidth="1"/>
-    <col min="100" max="100" width="11.08203125" customWidth="1"/>
-    <col min="101" max="101" width="13.75" customWidth="1"/>
-    <col min="108" max="108" width="15.5" customWidth="1"/>
-    <col min="112" max="112" width="9" hidden="1" customWidth="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" style="4" customWidth="1"/>
+    <col min="75" max="76" width="8.5" style="4" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" style="4" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" style="4" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="114" max="114" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>125</v>
       </c>
@@ -5570,209 +5612,215 @@
       <c r="AQ1" t="s">
         <v>164</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="AS1" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="AT1" t="s">
         <v>165</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>166</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>167</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>168</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>169</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>170</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>171</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>172</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>173</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>174</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>175</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>176</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>177</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>178</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>179</v>
       </c>
       <c r="BH1" t="s">
         <v>179</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
+        <v>179</v>
+      </c>
+      <c r="BK1" t="s">
         <v>180</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>181</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>182</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>183</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>184</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>185</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>186</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>187</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>188</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BT1" t="s">
         <v>189</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BU1" t="s">
         <v>190</v>
       </c>
-      <c r="BT1" s="4" t="s">
+      <c r="BV1" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="BU1" s="4" t="s">
+      <c r="BW1" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="BV1" s="4" t="s">
+      <c r="BX1" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="BW1" s="4" t="s">
+      <c r="BY1" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="BX1" s="4" t="s">
+      <c r="BZ1" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="BY1" s="4" t="s">
+      <c r="CA1" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CB1" t="s">
         <v>197</v>
       </c>
-      <c r="CA1" s="4" t="s">
+      <c r="CC1" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CD1" t="s">
         <v>199</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CE1" t="s">
         <v>200</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CF1" t="s">
         <v>201</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CG1" t="s">
         <v>202</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CH1" t="s">
         <v>203</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CI1" t="s">
         <v>204</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CJ1" t="s">
         <v>205</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CK1" t="s">
         <v>206</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CL1" t="s">
         <v>207</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CM1" t="s">
         <v>208</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CN1" t="s">
         <v>209</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CO1" t="s">
         <v>210</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CP1" t="s">
         <v>211</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CQ1" t="s">
         <v>212</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CR1" t="s">
         <v>189</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CS1" t="s">
         <v>213</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CT1" t="s">
         <v>214</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CU1" t="s">
         <v>215</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CV1" t="s">
         <v>216</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CW1" t="s">
         <v>217</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>218</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>219</v>
       </c>
       <c r="CX1" t="s">
         <v>218</v>
       </c>
       <c r="CY1" t="s">
+        <v>219</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>218</v>
+      </c>
+      <c r="DA1" t="s">
         <v>220</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DB1" t="s">
         <v>221</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DC1" t="s">
         <v>222</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DD1" t="s">
         <v>223</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DE1" t="s">
         <v>224</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DF1" t="s">
         <v>225</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DG1" t="s">
         <v>226</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DH1" t="s">
         <v>227</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DI1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5899,212 +5947,218 @@
       <c r="AQ2" t="s">
         <v>266</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="AS2" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="AT2" t="s">
         <v>267</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AU2" t="s">
         <v>268</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AV2" t="s">
         <v>269</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>270</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>271</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AY2" t="s">
         <v>272</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AZ2" t="s">
         <v>273</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BA2" t="s">
         <v>274</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BB2" t="s">
         <v>275</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BC2" t="s">
         <v>276</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BD2" t="s">
         <v>277</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BE2" t="s">
         <v>278</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BF2" t="s">
         <v>279</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BG2" t="s">
         <v>280</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BH2" t="s">
         <v>281</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BI2" t="s">
         <v>282</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BJ2" t="s">
         <v>283</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BK2" t="s">
         <v>284</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BL2" t="s">
         <v>285</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BM2" t="s">
         <v>286</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BN2" t="s">
         <v>287</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BO2" t="s">
         <v>78</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BP2" t="s">
         <v>288</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BQ2" t="s">
         <v>289</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BR2" t="s">
         <v>290</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BS2" t="s">
         <v>291</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BT2" t="s">
         <v>292</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BU2" t="s">
         <v>94</v>
       </c>
-      <c r="BT2" s="4" t="s">
+      <c r="BV2" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="BU2" s="4" t="s">
+      <c r="BW2" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="BV2" s="4" t="s">
+      <c r="BX2" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="BW2" s="4" t="s">
+      <c r="BY2" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="BX2" s="4" t="s">
+      <c r="BZ2" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="BY2" s="4" t="s">
+      <c r="CA2" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CB2" t="s">
         <v>299</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CC2" t="s">
         <v>300</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CD2" t="s">
         <v>301</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CE2" t="s">
         <v>302</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CF2" t="s">
         <v>303</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CG2" t="s">
         <v>304</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CH2" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CI2" t="s">
         <v>306</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CJ2" t="s">
         <v>307</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CK2" t="s">
         <v>308</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CL2" t="s">
         <v>309</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CM2" t="s">
         <v>310</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CN2" t="s">
         <v>311</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CO2" t="s">
         <v>312</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CP2" t="s">
         <v>313</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CQ2" t="s">
         <v>314</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CR2" t="s">
         <v>315</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CS2" t="s">
         <v>316</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CT2" t="s">
         <v>317</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CU2" t="s">
         <v>318</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CV2" t="s">
         <v>319</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CW2" t="s">
         <v>320</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CX2" t="s">
         <v>321</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CY2" t="s">
         <v>322</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CZ2" t="s">
         <v>323</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DA2" t="s">
         <v>324</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DB2" t="s">
         <v>325</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DC2" t="s">
         <v>326</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DD2" t="s">
         <v>327</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DE2" t="s">
         <v>328</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DF2" t="s">
         <v>329</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DG2" t="s">
         <v>330</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DH2" t="s">
         <v>331</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DI2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6231,182 +6285,182 @@
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AR3" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="AS3" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="AT3" t="s">
         <v>339</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>116</v>
       </c>
       <c r="AU3" t="s">
         <v>115</v>
       </c>
       <c r="AV3" t="s">
-        <v>340</v>
+        <v>116</v>
       </c>
       <c r="AW3" t="s">
         <v>115</v>
       </c>
       <c r="AX3" t="s">
-        <v>116</v>
+        <v>340</v>
       </c>
       <c r="AY3" t="s">
         <v>115</v>
       </c>
       <c r="AZ3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BA3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BB3" t="s">
         <v>117</v>
       </c>
       <c r="BC3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BD3" t="s">
         <v>117</v>
       </c>
-      <c r="BD3" t="s">
+      <c r="BE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF3" t="s">
         <v>116</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>339</v>
       </c>
       <c r="BG3" t="s">
         <v>115</v>
       </c>
       <c r="BH3" t="s">
-        <v>116</v>
+        <v>339</v>
       </c>
       <c r="BI3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BJ3" t="s">
         <v>116</v>
       </c>
       <c r="BK3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BM3" t="s">
         <v>117</v>
       </c>
-      <c r="BL3" t="s">
+      <c r="BN3" t="s">
         <v>117</v>
       </c>
-      <c r="BM3" t="s">
+      <c r="BO3" t="s">
         <v>118</v>
       </c>
-      <c r="BN3" t="s">
+      <c r="BP3" t="s">
         <v>118</v>
       </c>
-      <c r="BO3" t="s">
+      <c r="BQ3" t="s">
         <v>341</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="BR3" t="s">
         <v>342</v>
       </c>
-      <c r="BQ3" t="s">
+      <c r="BS3" t="s">
         <v>116</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="BT3" t="s">
         <v>116</v>
       </c>
-      <c r="BS3" t="s">
+      <c r="BU3" t="s">
         <v>115</v>
       </c>
-      <c r="BT3" s="4" t="s">
+      <c r="BV3" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="BU3" s="4" t="s">
+      <c r="BW3" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="BV3" s="4" t="s">
+      <c r="BX3" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="BW3" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="BX3" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="BY3" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="BZ3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>344</v>
+      <c r="BZ3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="CA3" s="4" t="s">
+        <v>343</v>
       </c>
       <c r="CB3" t="s">
         <v>123</v>
       </c>
       <c r="CC3" t="s">
-        <v>123</v>
+        <v>344</v>
       </c>
       <c r="CD3" t="s">
         <v>123</v>
       </c>
       <c r="CE3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CG3" t="s">
         <v>345</v>
       </c>
-      <c r="CF3" t="s">
+      <c r="CH3" t="s">
         <v>346</v>
       </c>
-      <c r="CG3" t="s">
+      <c r="CI3" t="s">
         <v>2</v>
       </c>
-      <c r="CH3" t="s">
+      <c r="CJ3" t="s">
         <v>347</v>
       </c>
-      <c r="CI3" t="s">
+      <c r="CK3" t="s">
         <v>347</v>
       </c>
-      <c r="CJ3" t="s">
+      <c r="CL3" t="s">
         <v>124</v>
       </c>
-      <c r="CK3" t="s">
+      <c r="CM3" t="s">
         <v>119</v>
       </c>
-      <c r="CL3" t="s">
+      <c r="CN3" t="s">
         <v>119</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>122</v>
       </c>
       <c r="CO3" t="s">
         <v>122</v>
       </c>
       <c r="CP3" t="s">
-        <v>344</v>
+        <v>122</v>
       </c>
       <c r="CQ3" t="s">
         <v>122</v>
       </c>
       <c r="CR3" t="s">
+        <v>344</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CT3" t="s">
         <v>115</v>
       </c>
-      <c r="CS3" t="s">
+      <c r="CU3" t="s">
         <v>124</v>
       </c>
-      <c r="CT3" t="s">
+      <c r="CV3" t="s">
         <v>348</v>
       </c>
-      <c r="CU3" t="s">
+      <c r="CW3" t="s">
         <v>349</v>
       </c>
-      <c r="CV3" t="s">
+      <c r="CX3" t="s">
         <v>349</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>348</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>348</v>
       </c>
       <c r="CY3" t="s">
         <v>348</v>
@@ -6418,10 +6472,10 @@
         <v>348</v>
       </c>
       <c r="DB3" t="s">
-        <v>115</v>
+        <v>348</v>
       </c>
       <c r="DC3" t="s">
-        <v>115</v>
+        <v>348</v>
       </c>
       <c r="DD3" t="s">
         <v>115</v>
@@ -6435,1303 +6489,1311 @@
       <c r="DG3" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="4" spans="1:111" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="DH3" t="s">
+        <v>115</v>
+      </c>
+      <c r="DI3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:113" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="8" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="BT8"/>
-    </row>
-    <row r="9" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="BT9"/>
-      <c r="CJ9" s="3"/>
-    </row>
-    <row r="10" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="CJ10" s="3"/>
-    </row>
-    <row r="11" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="CJ11" s="3"/>
-    </row>
-    <row r="12" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="CJ12" s="3"/>
-    </row>
-    <row r="13" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="CJ13" s="3"/>
-    </row>
-    <row r="14" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="BT14"/>
-    </row>
-    <row r="15" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="CJ15" s="3"/>
-    </row>
-    <row r="16" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="CJ16" s="3"/>
-    </row>
-    <row r="17" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ17" s="3"/>
-    </row>
-    <row r="18" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ18" s="3"/>
-    </row>
-    <row r="19" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT19"/>
-    </row>
-    <row r="20" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ20" s="3"/>
-    </row>
-    <row r="21" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ21" s="3"/>
-    </row>
-    <row r="22" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ22" s="3"/>
-    </row>
-    <row r="23" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ23" s="3"/>
-    </row>
-    <row r="26" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ26" s="3"/>
-    </row>
-    <row r="27" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ27" s="3"/>
-    </row>
-    <row r="28" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ28" s="3"/>
-    </row>
-    <row r="29" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ29" s="3"/>
-    </row>
-    <row r="30" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ30" s="3"/>
-    </row>
-    <row r="32" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT32"/>
-    </row>
-    <row r="33" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ33" s="3"/>
-    </row>
-    <row r="34" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ34" s="3"/>
-    </row>
-    <row r="35" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ35" s="3"/>
-    </row>
-    <row r="36" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ36" s="3"/>
-    </row>
-    <row r="40" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ40" s="3"/>
-    </row>
-    <row r="42" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT42"/>
-    </row>
-    <row r="43" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT43"/>
-      <c r="CJ43" s="3"/>
-    </row>
-    <row r="44" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ44" s="3"/>
-    </row>
-    <row r="45" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ45" s="3"/>
-    </row>
-    <row r="46" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ46" s="3"/>
-    </row>
-    <row r="47" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ47" s="3"/>
-    </row>
-    <row r="49" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT49"/>
-    </row>
-    <row r="50" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ50" s="3"/>
-    </row>
-    <row r="51" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ51" s="3"/>
-    </row>
-    <row r="53" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ53" s="3"/>
-    </row>
-    <row r="54" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ54" s="3"/>
-    </row>
-    <row r="56" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT56"/>
-    </row>
-    <row r="57" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ57" s="3"/>
-    </row>
-    <row r="60" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ60" s="3"/>
-    </row>
-    <row r="61" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ61" s="3"/>
-    </row>
-    <row r="64" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ64" s="3"/>
-    </row>
-    <row r="66" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ66" s="3"/>
-    </row>
-    <row r="68" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT68"/>
-    </row>
-    <row r="69" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ69" s="3"/>
-    </row>
-    <row r="70" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ70" s="3"/>
-    </row>
-    <row r="72" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ72" s="3"/>
-    </row>
-    <row r="73" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ73" s="3"/>
-    </row>
-    <row r="74" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ74" s="3"/>
-    </row>
-    <row r="79" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ79" s="3"/>
-    </row>
-    <row r="80" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ80" s="3"/>
-    </row>
-    <row r="83" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ83" s="3"/>
-    </row>
-    <row r="84" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ84" s="3"/>
-    </row>
-    <row r="88" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ88" s="3"/>
-    </row>
-    <row r="92" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ92" s="3"/>
-    </row>
-    <row r="94" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ94" s="3"/>
-    </row>
-    <row r="95" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ95" s="3"/>
-    </row>
-    <row r="97" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ97" s="3"/>
-    </row>
-    <row r="98" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ98" s="3"/>
-    </row>
-    <row r="100" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT100"/>
-    </row>
-    <row r="101" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT101"/>
-      <c r="CJ101" s="3"/>
-    </row>
-    <row r="102" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ102" s="3"/>
-    </row>
-    <row r="104" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ104" s="3"/>
-    </row>
-    <row r="113" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT113"/>
-    </row>
-    <row r="114" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT114"/>
-      <c r="CJ114" s="3"/>
-    </row>
-    <row r="115" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ115" s="3"/>
-    </row>
-    <row r="116" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ116" s="3"/>
-    </row>
-    <row r="117" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT117"/>
-    </row>
-    <row r="118" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT118"/>
-      <c r="CJ118" s="3"/>
-    </row>
-    <row r="119" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ119" s="3"/>
-    </row>
-    <row r="121" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT121"/>
-    </row>
-    <row r="122" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT122"/>
-      <c r="CJ122" s="3"/>
-    </row>
-    <row r="123" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ123" s="3"/>
-    </row>
-    <row r="125" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT125"/>
-    </row>
-    <row r="126" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ126" s="3"/>
-    </row>
-    <row r="129" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ129" s="3"/>
-    </row>
-    <row r="133" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ133" s="3"/>
-    </row>
-    <row r="135" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT135"/>
-    </row>
-    <row r="136" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ136" s="3"/>
-    </row>
-    <row r="143" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT143"/>
-    </row>
-    <row r="144" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ144" s="3"/>
-    </row>
-    <row r="145" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ145" s="3"/>
-    </row>
-    <row r="147" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT147"/>
-    </row>
-    <row r="148" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT148"/>
-      <c r="CJ148" s="3"/>
-    </row>
-    <row r="149" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ149" s="3"/>
-    </row>
-    <row r="155" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT155"/>
-    </row>
-    <row r="156" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT156"/>
-      <c r="CJ156" s="3"/>
-    </row>
-    <row r="157" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT157"/>
-      <c r="CJ157" s="3"/>
-    </row>
-    <row r="158" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ158" s="3"/>
-    </row>
-    <row r="163" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT163"/>
-    </row>
-    <row r="164" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT164"/>
-    </row>
-    <row r="168" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT168"/>
-    </row>
-    <row r="169" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ169" s="3"/>
-    </row>
-    <row r="170" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT170"/>
-    </row>
-    <row r="171" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ171" s="3"/>
-    </row>
-    <row r="181" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT181"/>
-    </row>
-    <row r="182" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ182" s="3"/>
-    </row>
-    <row r="184" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT184"/>
-    </row>
-    <row r="185" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ185" s="3"/>
-    </row>
-    <row r="193" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT193"/>
-    </row>
-    <row r="194" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ194" s="3"/>
-    </row>
-    <row r="198" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT198"/>
-    </row>
-    <row r="199" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ199" s="3"/>
-    </row>
-    <row r="201" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT201"/>
-    </row>
-    <row r="202" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ202" s="3"/>
-    </row>
-    <row r="218" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT218"/>
-    </row>
-    <row r="219" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT219"/>
-      <c r="CJ219" s="3"/>
-    </row>
-    <row r="220" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT220"/>
-      <c r="CJ220" s="3"/>
-    </row>
-    <row r="221" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT221"/>
-      <c r="CJ221" s="3"/>
-    </row>
-    <row r="222" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT222"/>
-    </row>
-    <row r="224" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT224"/>
-    </row>
-    <row r="225" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT225"/>
-      <c r="CJ225" s="3"/>
-    </row>
-    <row r="226" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT226"/>
-      <c r="CJ226" s="3"/>
-    </row>
-    <row r="227" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ227" s="3"/>
-    </row>
-    <row r="231" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT231"/>
-    </row>
-    <row r="232" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ232" s="3"/>
-    </row>
-    <row r="234" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT234"/>
-    </row>
-    <row r="235" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT235"/>
-      <c r="CJ235" s="3"/>
-    </row>
-    <row r="236" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT236"/>
-      <c r="CJ236" s="3"/>
-    </row>
-    <row r="237" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ237" s="3"/>
-    </row>
-    <row r="253" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT253"/>
-    </row>
-    <row r="254" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ254" s="3"/>
-    </row>
-    <row r="262" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ262" s="3"/>
-    </row>
-    <row r="263" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ263" s="3"/>
-    </row>
-    <row r="264" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ264" s="3"/>
-    </row>
-    <row r="265" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ265" s="3"/>
-    </row>
-    <row r="266" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ266" s="3"/>
-    </row>
-    <row r="268" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT268"/>
-    </row>
-    <row r="269" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ269" s="3"/>
-    </row>
-    <row r="270" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT270"/>
-    </row>
-    <row r="271" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT271"/>
-      <c r="CJ271" s="3"/>
-    </row>
-    <row r="272" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ272" s="3"/>
-    </row>
-    <row r="274" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT274"/>
-    </row>
-    <row r="275" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT275"/>
-      <c r="CJ275" s="3"/>
-    </row>
-    <row r="276" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT276"/>
-      <c r="CJ276" s="3"/>
-    </row>
-    <row r="277" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ277" s="3"/>
-    </row>
-    <row r="279" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ279" s="3"/>
-    </row>
-    <row r="281" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ281" s="3"/>
-    </row>
-    <row r="283" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ283" s="3"/>
-    </row>
-    <row r="286" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ286" s="3"/>
-    </row>
-    <row r="287" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ287" s="3"/>
-    </row>
-    <row r="288" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ288" s="3"/>
-    </row>
-    <row r="289" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ289" s="3"/>
-    </row>
-    <row r="290" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ290" s="3"/>
-    </row>
-    <row r="291" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ291" s="3"/>
-    </row>
-    <row r="292" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT292"/>
-    </row>
-    <row r="293" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT293"/>
-      <c r="CJ293" s="3"/>
-    </row>
-    <row r="294" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT294"/>
-      <c r="CJ294" s="3"/>
-    </row>
-    <row r="295" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ295" s="3"/>
-    </row>
-    <row r="296" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ296" s="3"/>
-    </row>
-    <row r="297" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ297" s="3"/>
-    </row>
-    <row r="298" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ298" s="3"/>
-    </row>
-    <row r="300" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ300" s="3"/>
-    </row>
-    <row r="301" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ301" s="3"/>
-    </row>
-    <row r="302" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT302"/>
-    </row>
-    <row r="303" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT303"/>
-      <c r="CJ303" s="3"/>
-    </row>
-    <row r="304" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT304"/>
-      <c r="CJ304" s="3"/>
-    </row>
-    <row r="305" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ305" s="3"/>
-    </row>
-    <row r="306" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ306" s="3"/>
-    </row>
-    <row r="308" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ308" s="3"/>
-    </row>
-    <row r="309" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ309" s="3"/>
-    </row>
-    <row r="310" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT310"/>
-      <c r="CJ310" s="3"/>
-    </row>
-    <row r="311" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT311"/>
-      <c r="CJ311" s="3"/>
-    </row>
-    <row r="312" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ312" s="3"/>
-    </row>
-    <row r="313" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ313" s="3"/>
-    </row>
-    <row r="314" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ314" s="3"/>
-    </row>
-    <row r="316" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT316"/>
-      <c r="CJ316" s="3"/>
-    </row>
-    <row r="317" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ317" s="3"/>
-    </row>
-    <row r="318" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ318" s="3"/>
-    </row>
-    <row r="320" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT320"/>
-      <c r="CJ320" s="3"/>
-    </row>
-    <row r="321" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT321"/>
-      <c r="CJ321" s="3"/>
-    </row>
-    <row r="322" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ322" s="3"/>
-    </row>
-    <row r="324" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ324" s="3"/>
-    </row>
-    <row r="326" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ326" s="3"/>
-    </row>
-    <row r="329" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ329" s="3"/>
-    </row>
-    <row r="330" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ330" s="3"/>
-    </row>
-    <row r="334" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT334"/>
-    </row>
-    <row r="335" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT335"/>
-      <c r="CJ335" s="3"/>
-    </row>
-    <row r="336" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT336"/>
-      <c r="CJ336" s="3"/>
-    </row>
-    <row r="337" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ337" s="3"/>
-    </row>
-    <row r="338" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ338" s="3"/>
-    </row>
-    <row r="339" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT339"/>
-    </row>
-    <row r="340" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ340" s="3"/>
-    </row>
-    <row r="342" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ342" s="3"/>
-    </row>
-    <row r="343" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ343" s="3"/>
-    </row>
-    <row r="345" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ345" s="3"/>
-    </row>
-    <row r="346" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ346" s="3"/>
-    </row>
-    <row r="347" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ347" s="3"/>
-    </row>
-    <row r="348" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ348" s="3"/>
-    </row>
-    <row r="349" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ349" s="3"/>
-    </row>
-    <row r="350" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ350" s="3"/>
-    </row>
-    <row r="351" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ351" s="3"/>
-    </row>
-    <row r="353" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT353"/>
-    </row>
-    <row r="354" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ354" s="3"/>
-    </row>
-    <row r="355" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ355" s="3"/>
-    </row>
-    <row r="388" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS388" s="5"/>
-      <c r="BT388" s="6"/>
-    </row>
-    <row r="389" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+    </row>
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="BV8"/>
+    </row>
+    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="BV9"/>
+      <c r="CL9" s="3"/>
+    </row>
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="CL10" s="3"/>
+    </row>
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="CL11" s="3"/>
+    </row>
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="CL12" s="3"/>
+    </row>
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="CL13" s="3"/>
+    </row>
+    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="BV14"/>
+    </row>
+    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="CL15" s="3"/>
+    </row>
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="CL16" s="3"/>
+    </row>
+    <row r="17" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL17" s="3"/>
+    </row>
+    <row r="18" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL18" s="3"/>
+    </row>
+    <row r="19" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV19"/>
+    </row>
+    <row r="20" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL20" s="3"/>
+    </row>
+    <row r="21" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL21" s="3"/>
+    </row>
+    <row r="22" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL22" s="3"/>
+    </row>
+    <row r="23" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL23" s="3"/>
+    </row>
+    <row r="26" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL26" s="3"/>
+    </row>
+    <row r="27" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL27" s="3"/>
+    </row>
+    <row r="28" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL28" s="3"/>
+    </row>
+    <row r="29" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL29" s="3"/>
+    </row>
+    <row r="30" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL30" s="3"/>
+    </row>
+    <row r="32" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV32"/>
+    </row>
+    <row r="33" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL33" s="3"/>
+    </row>
+    <row r="34" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL34" s="3"/>
+    </row>
+    <row r="35" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL35" s="3"/>
+    </row>
+    <row r="36" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL36" s="3"/>
+    </row>
+    <row r="40" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL40" s="3"/>
+    </row>
+    <row r="42" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV42"/>
+    </row>
+    <row r="43" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV43"/>
+      <c r="CL43" s="3"/>
+    </row>
+    <row r="44" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL44" s="3"/>
+    </row>
+    <row r="45" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL45" s="3"/>
+    </row>
+    <row r="46" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL46" s="3"/>
+    </row>
+    <row r="47" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL47" s="3"/>
+    </row>
+    <row r="49" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV49"/>
+    </row>
+    <row r="50" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL50" s="3"/>
+    </row>
+    <row r="51" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL51" s="3"/>
+    </row>
+    <row r="53" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL53" s="3"/>
+    </row>
+    <row r="54" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL54" s="3"/>
+    </row>
+    <row r="56" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV56"/>
+    </row>
+    <row r="57" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL57" s="3"/>
+    </row>
+    <row r="60" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL60" s="3"/>
+    </row>
+    <row r="61" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL61" s="3"/>
+    </row>
+    <row r="64" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL64" s="3"/>
+    </row>
+    <row r="66" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL66" s="3"/>
+    </row>
+    <row r="68" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV68"/>
+    </row>
+    <row r="69" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL69" s="3"/>
+    </row>
+    <row r="70" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL70" s="3"/>
+    </row>
+    <row r="72" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL72" s="3"/>
+    </row>
+    <row r="73" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL73" s="3"/>
+    </row>
+    <row r="74" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL74" s="3"/>
+    </row>
+    <row r="79" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL79" s="3"/>
+    </row>
+    <row r="80" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL80" s="3"/>
+    </row>
+    <row r="83" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL83" s="3"/>
+    </row>
+    <row r="84" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL84" s="3"/>
+    </row>
+    <row r="88" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL88" s="3"/>
+    </row>
+    <row r="92" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL92" s="3"/>
+    </row>
+    <row r="94" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL94" s="3"/>
+    </row>
+    <row r="95" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL95" s="3"/>
+    </row>
+    <row r="97" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL97" s="3"/>
+    </row>
+    <row r="98" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL98" s="3"/>
+    </row>
+    <row r="100" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV100"/>
+    </row>
+    <row r="101" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV101"/>
+      <c r="CL101" s="3"/>
+    </row>
+    <row r="102" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL102" s="3"/>
+    </row>
+    <row r="104" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL104" s="3"/>
+    </row>
+    <row r="113" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV113"/>
+    </row>
+    <row r="114" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV114"/>
+      <c r="CL114" s="3"/>
+    </row>
+    <row r="115" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL115" s="3"/>
+    </row>
+    <row r="116" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL116" s="3"/>
+    </row>
+    <row r="117" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV117"/>
+    </row>
+    <row r="118" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV118"/>
+      <c r="CL118" s="3"/>
+    </row>
+    <row r="119" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL119" s="3"/>
+    </row>
+    <row r="121" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV121"/>
+    </row>
+    <row r="122" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV122"/>
+      <c r="CL122" s="3"/>
+    </row>
+    <row r="123" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL123" s="3"/>
+    </row>
+    <row r="125" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV125"/>
+    </row>
+    <row r="126" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL126" s="3"/>
+    </row>
+    <row r="129" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL129" s="3"/>
+    </row>
+    <row r="133" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL133" s="3"/>
+    </row>
+    <row r="135" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV135"/>
+    </row>
+    <row r="136" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL136" s="3"/>
+    </row>
+    <row r="143" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV143"/>
+    </row>
+    <row r="144" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL144" s="3"/>
+    </row>
+    <row r="145" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL145" s="3"/>
+    </row>
+    <row r="147" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV147"/>
+    </row>
+    <row r="148" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV148"/>
+      <c r="CL148" s="3"/>
+    </row>
+    <row r="149" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL149" s="3"/>
+    </row>
+    <row r="155" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV155"/>
+    </row>
+    <row r="156" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV156"/>
+      <c r="CL156" s="3"/>
+    </row>
+    <row r="157" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV157"/>
+      <c r="CL157" s="3"/>
+    </row>
+    <row r="158" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL158" s="3"/>
+    </row>
+    <row r="163" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV163"/>
+    </row>
+    <row r="164" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV164"/>
+    </row>
+    <row r="168" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV168"/>
+    </row>
+    <row r="169" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL169" s="3"/>
+    </row>
+    <row r="170" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV170"/>
+    </row>
+    <row r="171" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL171" s="3"/>
+    </row>
+    <row r="181" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV181"/>
+    </row>
+    <row r="182" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL182" s="3"/>
+    </row>
+    <row r="184" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV184"/>
+    </row>
+    <row r="185" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL185" s="3"/>
+    </row>
+    <row r="193" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV193"/>
+    </row>
+    <row r="194" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL194" s="3"/>
+    </row>
+    <row r="198" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV198"/>
+    </row>
+    <row r="199" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL199" s="3"/>
+    </row>
+    <row r="201" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV201"/>
+    </row>
+    <row r="202" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL202" s="3"/>
+    </row>
+    <row r="218" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV218"/>
+    </row>
+    <row r="219" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV219"/>
+      <c r="CL219" s="3"/>
+    </row>
+    <row r="220" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV220"/>
+      <c r="CL220" s="3"/>
+    </row>
+    <row r="221" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV221"/>
+      <c r="CL221" s="3"/>
+    </row>
+    <row r="222" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV222"/>
+    </row>
+    <row r="224" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV224"/>
+    </row>
+    <row r="225" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV225"/>
+      <c r="CL225" s="3"/>
+    </row>
+    <row r="226" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV226"/>
+      <c r="CL226" s="3"/>
+    </row>
+    <row r="227" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL227" s="3"/>
+    </row>
+    <row r="231" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV231"/>
+    </row>
+    <row r="232" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL232" s="3"/>
+    </row>
+    <row r="234" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV234"/>
+    </row>
+    <row r="235" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV235"/>
+      <c r="CL235" s="3"/>
+    </row>
+    <row r="236" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV236"/>
+      <c r="CL236" s="3"/>
+    </row>
+    <row r="237" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL237" s="3"/>
+    </row>
+    <row r="253" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV253"/>
+    </row>
+    <row r="254" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL254" s="3"/>
+    </row>
+    <row r="262" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL262" s="3"/>
+    </row>
+    <row r="263" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL263" s="3"/>
+    </row>
+    <row r="264" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL264" s="3"/>
+    </row>
+    <row r="265" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL265" s="3"/>
+    </row>
+    <row r="266" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL266" s="3"/>
+    </row>
+    <row r="268" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV268"/>
+    </row>
+    <row r="269" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL269" s="3"/>
+    </row>
+    <row r="270" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV270"/>
+    </row>
+    <row r="271" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV271"/>
+      <c r="CL271" s="3"/>
+    </row>
+    <row r="272" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL272" s="3"/>
+    </row>
+    <row r="274" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV274"/>
+    </row>
+    <row r="275" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV275"/>
+      <c r="CL275" s="3"/>
+    </row>
+    <row r="276" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV276"/>
+      <c r="CL276" s="3"/>
+    </row>
+    <row r="277" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL277" s="3"/>
+    </row>
+    <row r="279" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL279" s="3"/>
+    </row>
+    <row r="281" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL281" s="3"/>
+    </row>
+    <row r="283" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL283" s="3"/>
+    </row>
+    <row r="286" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL286" s="3"/>
+    </row>
+    <row r="287" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL287" s="3"/>
+    </row>
+    <row r="288" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL288" s="3"/>
+    </row>
+    <row r="289" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL289" s="3"/>
+    </row>
+    <row r="290" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL290" s="3"/>
+    </row>
+    <row r="291" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL291" s="3"/>
+    </row>
+    <row r="292" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV292"/>
+    </row>
+    <row r="293" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV293"/>
+      <c r="CL293" s="3"/>
+    </row>
+    <row r="294" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV294"/>
+      <c r="CL294" s="3"/>
+    </row>
+    <row r="295" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL295" s="3"/>
+    </row>
+    <row r="296" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL296" s="3"/>
+    </row>
+    <row r="297" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL297" s="3"/>
+    </row>
+    <row r="298" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL298" s="3"/>
+    </row>
+    <row r="300" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL300" s="3"/>
+    </row>
+    <row r="301" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL301" s="3"/>
+    </row>
+    <row r="302" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV302"/>
+    </row>
+    <row r="303" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV303"/>
+      <c r="CL303" s="3"/>
+    </row>
+    <row r="304" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV304"/>
+      <c r="CL304" s="3"/>
+    </row>
+    <row r="305" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL305" s="3"/>
+    </row>
+    <row r="306" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL306" s="3"/>
+    </row>
+    <row r="308" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL308" s="3"/>
+    </row>
+    <row r="309" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL309" s="3"/>
+    </row>
+    <row r="310" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV310"/>
+      <c r="CL310" s="3"/>
+    </row>
+    <row r="311" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV311"/>
+      <c r="CL311" s="3"/>
+    </row>
+    <row r="312" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL312" s="3"/>
+    </row>
+    <row r="313" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL313" s="3"/>
+    </row>
+    <row r="314" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL314" s="3"/>
+    </row>
+    <row r="316" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV316"/>
+      <c r="CL316" s="3"/>
+    </row>
+    <row r="317" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL317" s="3"/>
+    </row>
+    <row r="318" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL318" s="3"/>
+    </row>
+    <row r="320" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV320"/>
+      <c r="CL320" s="3"/>
+    </row>
+    <row r="321" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV321"/>
+      <c r="CL321" s="3"/>
+    </row>
+    <row r="322" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL322" s="3"/>
+    </row>
+    <row r="324" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL324" s="3"/>
+    </row>
+    <row r="326" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL326" s="3"/>
+    </row>
+    <row r="329" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL329" s="3"/>
+    </row>
+    <row r="330" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL330" s="3"/>
+    </row>
+    <row r="334" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV334"/>
+    </row>
+    <row r="335" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV335"/>
+      <c r="CL335" s="3"/>
+    </row>
+    <row r="336" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV336"/>
+      <c r="CL336" s="3"/>
+    </row>
+    <row r="337" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL337" s="3"/>
+    </row>
+    <row r="338" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL338" s="3"/>
+    </row>
+    <row r="339" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV339"/>
+    </row>
+    <row r="340" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL340" s="3"/>
+    </row>
+    <row r="342" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL342" s="3"/>
+    </row>
+    <row r="343" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL343" s="3"/>
+    </row>
+    <row r="345" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL345" s="3"/>
+    </row>
+    <row r="346" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL346" s="3"/>
+    </row>
+    <row r="347" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL347" s="3"/>
+    </row>
+    <row r="348" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL348" s="3"/>
+    </row>
+    <row r="349" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL349" s="3"/>
+    </row>
+    <row r="350" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL350" s="3"/>
+    </row>
+    <row r="351" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL351" s="3"/>
+    </row>
+    <row r="353" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV353"/>
+    </row>
+    <row r="354" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL354" s="3"/>
+    </row>
+    <row r="355" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL355" s="3"/>
+    </row>
+    <row r="388" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU388" s="5"/>
+      <c r="BV388" s="6"/>
+    </row>
+    <row r="389" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H389" s="5"/>
-      <c r="CJ389" s="5"/>
-    </row>
-    <row r="395" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT395"/>
-    </row>
-    <row r="396" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT396"/>
-      <c r="CJ396" s="3"/>
-    </row>
-    <row r="397" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT397"/>
-      <c r="CJ397" s="3"/>
-    </row>
-    <row r="398" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ398" s="3"/>
-    </row>
-    <row r="415" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT415"/>
-    </row>
-    <row r="416" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ416" s="3"/>
-    </row>
-    <row r="448" spans="72:72" x14ac:dyDescent="0.25">
-      <c r="BT448"/>
-    </row>
-    <row r="449" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT449"/>
-      <c r="CJ449" s="3"/>
-    </row>
-    <row r="450" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ450" s="3"/>
-    </row>
-    <row r="466" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT466"/>
-    </row>
-    <row r="467" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ467" s="3"/>
-    </row>
-    <row r="473" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT473"/>
-    </row>
-    <row r="474" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT474"/>
-      <c r="CJ474" s="3"/>
-    </row>
-    <row r="475" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ475" s="3"/>
-    </row>
-    <row r="480" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT480"/>
-    </row>
-    <row r="481" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT481"/>
-      <c r="CJ481" s="3"/>
-    </row>
-    <row r="482" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT482"/>
-      <c r="CJ482" s="3"/>
-    </row>
-    <row r="483" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT483"/>
-      <c r="CJ483" s="3"/>
-    </row>
-    <row r="484" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT484"/>
-      <c r="CJ484" s="3"/>
-    </row>
-    <row r="485" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT485"/>
-      <c r="CJ485" s="3"/>
-    </row>
-    <row r="486" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT486"/>
-      <c r="CJ486" s="3"/>
-    </row>
-    <row r="487" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT487"/>
-      <c r="CJ487" s="3"/>
-    </row>
-    <row r="488" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT488"/>
-      <c r="CJ488" s="3"/>
-    </row>
-    <row r="489" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT489"/>
-      <c r="CJ489" s="3"/>
-    </row>
-    <row r="490" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT490"/>
-      <c r="CJ490" s="3"/>
-    </row>
-    <row r="491" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT491"/>
-      <c r="CJ491" s="3"/>
-    </row>
-    <row r="492" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT492"/>
-      <c r="CJ492" s="3"/>
-    </row>
-    <row r="493" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT493"/>
-      <c r="CJ493" s="3"/>
-    </row>
-    <row r="494" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT494"/>
-      <c r="CJ494" s="3"/>
-    </row>
-    <row r="495" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT495"/>
-      <c r="CJ495" s="3"/>
-    </row>
-    <row r="496" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ496" s="3"/>
-    </row>
-    <row r="500" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT500"/>
-    </row>
-    <row r="501" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT501"/>
-      <c r="CJ501" s="3"/>
-    </row>
-    <row r="502" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ502" s="3"/>
-    </row>
-    <row r="503" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT503"/>
-    </row>
-    <row r="504" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ504" s="3"/>
-    </row>
-    <row r="507" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT507"/>
-    </row>
-    <row r="508" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT508"/>
-      <c r="CJ508" s="3"/>
-    </row>
-    <row r="509" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ509" s="3"/>
-    </row>
-    <row r="540" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT540"/>
-    </row>
-    <row r="541" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT541"/>
-      <c r="CJ541" s="3"/>
-    </row>
-    <row r="542" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT542"/>
-      <c r="CJ542" s="3"/>
-    </row>
-    <row r="543" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT543"/>
-      <c r="CJ543" s="3"/>
-    </row>
-    <row r="544" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT544"/>
-      <c r="CJ544" s="3"/>
-    </row>
-    <row r="545" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT545"/>
-      <c r="CJ545" s="3"/>
-    </row>
-    <row r="546" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT546"/>
-      <c r="CJ546" s="3"/>
-    </row>
-    <row r="547" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT547"/>
-      <c r="CJ547" s="3"/>
-    </row>
-    <row r="548" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ548" s="3"/>
-    </row>
-    <row r="550" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT550"/>
-    </row>
-    <row r="551" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ551" s="3"/>
-    </row>
-    <row r="555" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT555"/>
-    </row>
-    <row r="556" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ556" s="3"/>
-    </row>
-    <row r="559" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT559"/>
-    </row>
-    <row r="560" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT560"/>
-      <c r="CJ560" s="3"/>
-    </row>
-    <row r="561" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT561"/>
-      <c r="CJ561" s="3"/>
-    </row>
-    <row r="562" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT562"/>
-      <c r="CJ562" s="3"/>
-    </row>
-    <row r="563" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ563" s="3"/>
-    </row>
-    <row r="570" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT570"/>
-    </row>
-    <row r="571" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ571" s="3"/>
-    </row>
-    <row r="574" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT574"/>
-    </row>
-    <row r="575" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT575"/>
-      <c r="CJ575" s="3"/>
-    </row>
-    <row r="576" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT576"/>
-      <c r="CJ576" s="3"/>
-    </row>
-    <row r="577" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT577"/>
-      <c r="CJ577" s="3"/>
-    </row>
-    <row r="578" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ578" s="3"/>
-    </row>
-    <row r="580" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT580"/>
-    </row>
-    <row r="581" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT581"/>
-      <c r="CJ581" s="3"/>
-    </row>
-    <row r="582" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ582" s="3"/>
-    </row>
-    <row r="583" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ583">
+      <c r="CL389" s="5"/>
+    </row>
+    <row r="395" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV395"/>
+    </row>
+    <row r="396" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV396"/>
+      <c r="CL396" s="3"/>
+    </row>
+    <row r="397" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV397"/>
+      <c r="CL397" s="3"/>
+    </row>
+    <row r="398" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL398" s="3"/>
+    </row>
+    <row r="415" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV415"/>
+    </row>
+    <row r="416" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL416" s="3"/>
+    </row>
+    <row r="448" spans="74:74" x14ac:dyDescent="0.25">
+      <c r="BV448"/>
+    </row>
+    <row r="449" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV449"/>
+      <c r="CL449" s="3"/>
+    </row>
+    <row r="450" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL450" s="3"/>
+    </row>
+    <row r="466" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV466"/>
+    </row>
+    <row r="467" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL467" s="3"/>
+    </row>
+    <row r="473" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV473"/>
+    </row>
+    <row r="474" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV474"/>
+      <c r="CL474" s="3"/>
+    </row>
+    <row r="475" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL475" s="3"/>
+    </row>
+    <row r="480" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV480"/>
+    </row>
+    <row r="481" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV481"/>
+      <c r="CL481" s="3"/>
+    </row>
+    <row r="482" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV482"/>
+      <c r="CL482" s="3"/>
+    </row>
+    <row r="483" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV483"/>
+      <c r="CL483" s="3"/>
+    </row>
+    <row r="484" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV484"/>
+      <c r="CL484" s="3"/>
+    </row>
+    <row r="485" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV485"/>
+      <c r="CL485" s="3"/>
+    </row>
+    <row r="486" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV486"/>
+      <c r="CL486" s="3"/>
+    </row>
+    <row r="487" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV487"/>
+      <c r="CL487" s="3"/>
+    </row>
+    <row r="488" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV488"/>
+      <c r="CL488" s="3"/>
+    </row>
+    <row r="489" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV489"/>
+      <c r="CL489" s="3"/>
+    </row>
+    <row r="490" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV490"/>
+      <c r="CL490" s="3"/>
+    </row>
+    <row r="491" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV491"/>
+      <c r="CL491" s="3"/>
+    </row>
+    <row r="492" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV492"/>
+      <c r="CL492" s="3"/>
+    </row>
+    <row r="493" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV493"/>
+      <c r="CL493" s="3"/>
+    </row>
+    <row r="494" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV494"/>
+      <c r="CL494" s="3"/>
+    </row>
+    <row r="495" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV495"/>
+      <c r="CL495" s="3"/>
+    </row>
+    <row r="496" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL496" s="3"/>
+    </row>
+    <row r="500" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV500"/>
+    </row>
+    <row r="501" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV501"/>
+      <c r="CL501" s="3"/>
+    </row>
+    <row r="502" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL502" s="3"/>
+    </row>
+    <row r="503" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV503"/>
+    </row>
+    <row r="504" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL504" s="3"/>
+    </row>
+    <row r="507" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV507"/>
+    </row>
+    <row r="508" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV508"/>
+      <c r="CL508" s="3"/>
+    </row>
+    <row r="509" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL509" s="3"/>
+    </row>
+    <row r="540" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV540"/>
+    </row>
+    <row r="541" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV541"/>
+      <c r="CL541" s="3"/>
+    </row>
+    <row r="542" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV542"/>
+      <c r="CL542" s="3"/>
+    </row>
+    <row r="543" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV543"/>
+      <c r="CL543" s="3"/>
+    </row>
+    <row r="544" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV544"/>
+      <c r="CL544" s="3"/>
+    </row>
+    <row r="545" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV545"/>
+      <c r="CL545" s="3"/>
+    </row>
+    <row r="546" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV546"/>
+      <c r="CL546" s="3"/>
+    </row>
+    <row r="547" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV547"/>
+      <c r="CL547" s="3"/>
+    </row>
+    <row r="548" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL548" s="3"/>
+    </row>
+    <row r="550" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV550"/>
+    </row>
+    <row r="551" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL551" s="3"/>
+    </row>
+    <row r="555" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV555"/>
+    </row>
+    <row r="556" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL556" s="3"/>
+    </row>
+    <row r="559" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV559"/>
+    </row>
+    <row r="560" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV560"/>
+      <c r="CL560" s="3"/>
+    </row>
+    <row r="561" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV561"/>
+      <c r="CL561" s="3"/>
+    </row>
+    <row r="562" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV562"/>
+      <c r="CL562" s="3"/>
+    </row>
+    <row r="563" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL563" s="3"/>
+    </row>
+    <row r="570" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV570"/>
+    </row>
+    <row r="571" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL571" s="3"/>
+    </row>
+    <row r="574" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV574"/>
+    </row>
+    <row r="575" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV575"/>
+      <c r="CL575" s="3"/>
+    </row>
+    <row r="576" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV576"/>
+      <c r="CL576" s="3"/>
+    </row>
+    <row r="577" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV577"/>
+      <c r="CL577" s="3"/>
+    </row>
+    <row r="578" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL578" s="3"/>
+    </row>
+    <row r="580" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV580"/>
+    </row>
+    <row r="581" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV581"/>
+      <c r="CL581" s="3"/>
+    </row>
+    <row r="582" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL582" s="3"/>
+    </row>
+    <row r="583" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL583">
         <v>0.15</v>
       </c>
     </row>
-    <row r="585" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ585">
+    <row r="585" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL585">
         <v>0.2</v>
       </c>
     </row>
-    <row r="586" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ586">
+    <row r="586" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL586">
         <v>0.1</v>
       </c>
     </row>
-    <row r="588" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ588">
+    <row r="588" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL588">
         <v>0.2</v>
       </c>
     </row>
-    <row r="595" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ595">
+    <row r="595" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL595">
         <v>1</v>
       </c>
     </row>
-    <row r="597" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ597">
+    <row r="597" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL597">
         <v>0.4</v>
       </c>
     </row>
-    <row r="598" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ598">
+    <row r="598" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL598">
         <v>0.6</v>
       </c>
     </row>
-    <row r="601" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ601">
+    <row r="601" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL601">
         <v>0.5</v>
       </c>
     </row>
-    <row r="602" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ602">
+    <row r="602" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL602">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="603" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ603">
+    <row r="603" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL603">
         <v>0.2</v>
       </c>
     </row>
-    <row r="606" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT606"/>
-    </row>
-    <row r="607" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT607"/>
-      <c r="CJ607" s="3"/>
-    </row>
-    <row r="608" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT608"/>
-      <c r="CJ608" s="3"/>
-    </row>
-    <row r="609" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT609"/>
-      <c r="CJ609" s="3"/>
-    </row>
-    <row r="610" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT610"/>
-      <c r="CJ610" s="3"/>
-    </row>
-    <row r="611" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT611"/>
-      <c r="CJ611" s="3"/>
-    </row>
-    <row r="612" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT612"/>
-      <c r="CJ612" s="3"/>
-    </row>
-    <row r="613" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT613"/>
-      <c r="CJ613" s="3"/>
-    </row>
-    <row r="614" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT614"/>
-      <c r="CJ614" s="3"/>
-    </row>
-    <row r="615" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ615" s="3"/>
-    </row>
-    <row r="616" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT616"/>
-    </row>
-    <row r="617" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ617" s="3"/>
-    </row>
-    <row r="626" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT626"/>
-    </row>
-    <row r="627" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT627"/>
-      <c r="CJ627" s="3"/>
-    </row>
-    <row r="628" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT628"/>
-      <c r="CJ628" s="3"/>
-    </row>
-    <row r="629" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT629"/>
-      <c r="CJ629" s="3"/>
-    </row>
-    <row r="630" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT630"/>
-      <c r="CJ630" s="3"/>
-    </row>
-    <row r="631" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT631"/>
-      <c r="CJ631" s="3"/>
-    </row>
-    <row r="632" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT632"/>
-      <c r="CJ632" s="3"/>
-    </row>
-    <row r="633" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT633"/>
-      <c r="CJ633" s="3"/>
-    </row>
-    <row r="634" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ634" s="3"/>
-    </row>
-    <row r="635" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT635"/>
-    </row>
-    <row r="636" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ636" s="3"/>
-    </row>
-    <row r="641" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT641"/>
-    </row>
-    <row r="642" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT642"/>
-      <c r="CJ642" s="3"/>
-    </row>
-    <row r="643" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ643" s="3"/>
-    </row>
-    <row r="644" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT644"/>
-    </row>
-    <row r="645" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT645"/>
-      <c r="CJ645" s="3"/>
-    </row>
-    <row r="646" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ646" s="3"/>
-    </row>
-    <row r="647" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT647"/>
-    </row>
-    <row r="648" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT648"/>
-      <c r="CJ648" s="3"/>
-    </row>
-    <row r="649" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT649"/>
-      <c r="CJ649" s="3"/>
-    </row>
-    <row r="650" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT650"/>
-      <c r="CJ650" s="3"/>
-    </row>
-    <row r="651" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ651" s="3"/>
-    </row>
-    <row r="655" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT655"/>
-    </row>
-    <row r="656" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT656"/>
-      <c r="CJ656" s="3"/>
-    </row>
-    <row r="657" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT657"/>
-      <c r="CJ657" s="3"/>
-    </row>
-    <row r="658" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ658" s="3"/>
-    </row>
-    <row r="659" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT659"/>
-    </row>
-    <row r="660" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ660" s="3"/>
-    </row>
-    <row r="661" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS661" s="5"/>
-      <c r="BT661" s="6"/>
-    </row>
-    <row r="662" spans="8:88" x14ac:dyDescent="0.25">
+    <row r="606" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV606"/>
+    </row>
+    <row r="607" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV607"/>
+      <c r="CL607" s="3"/>
+    </row>
+    <row r="608" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV608"/>
+      <c r="CL608" s="3"/>
+    </row>
+    <row r="609" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV609"/>
+      <c r="CL609" s="3"/>
+    </row>
+    <row r="610" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV610"/>
+      <c r="CL610" s="3"/>
+    </row>
+    <row r="611" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV611"/>
+      <c r="CL611" s="3"/>
+    </row>
+    <row r="612" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV612"/>
+      <c r="CL612" s="3"/>
+    </row>
+    <row r="613" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV613"/>
+      <c r="CL613" s="3"/>
+    </row>
+    <row r="614" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV614"/>
+      <c r="CL614" s="3"/>
+    </row>
+    <row r="615" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL615" s="3"/>
+    </row>
+    <row r="616" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV616"/>
+    </row>
+    <row r="617" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL617" s="3"/>
+    </row>
+    <row r="626" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV626"/>
+    </row>
+    <row r="627" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV627"/>
+      <c r="CL627" s="3"/>
+    </row>
+    <row r="628" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV628"/>
+      <c r="CL628" s="3"/>
+    </row>
+    <row r="629" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV629"/>
+      <c r="CL629" s="3"/>
+    </row>
+    <row r="630" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV630"/>
+      <c r="CL630" s="3"/>
+    </row>
+    <row r="631" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV631"/>
+      <c r="CL631" s="3"/>
+    </row>
+    <row r="632" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV632"/>
+      <c r="CL632" s="3"/>
+    </row>
+    <row r="633" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV633"/>
+      <c r="CL633" s="3"/>
+    </row>
+    <row r="634" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL634" s="3"/>
+    </row>
+    <row r="635" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV635"/>
+    </row>
+    <row r="636" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL636" s="3"/>
+    </row>
+    <row r="641" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV641"/>
+    </row>
+    <row r="642" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV642"/>
+      <c r="CL642" s="3"/>
+    </row>
+    <row r="643" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL643" s="3"/>
+    </row>
+    <row r="644" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV644"/>
+    </row>
+    <row r="645" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV645"/>
+      <c r="CL645" s="3"/>
+    </row>
+    <row r="646" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL646" s="3"/>
+    </row>
+    <row r="647" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV647"/>
+    </row>
+    <row r="648" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV648"/>
+      <c r="CL648" s="3"/>
+    </row>
+    <row r="649" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV649"/>
+      <c r="CL649" s="3"/>
+    </row>
+    <row r="650" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV650"/>
+      <c r="CL650" s="3"/>
+    </row>
+    <row r="651" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL651" s="3"/>
+    </row>
+    <row r="655" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV655"/>
+    </row>
+    <row r="656" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV656"/>
+      <c r="CL656" s="3"/>
+    </row>
+    <row r="657" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV657"/>
+      <c r="CL657" s="3"/>
+    </row>
+    <row r="658" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL658" s="3"/>
+    </row>
+    <row r="659" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV659"/>
+    </row>
+    <row r="660" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL660" s="3"/>
+    </row>
+    <row r="661" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU661" s="5"/>
+      <c r="BV661" s="6"/>
+    </row>
+    <row r="662" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H662" s="5"/>
-      <c r="CJ662" s="5"/>
-    </row>
-    <row r="679" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT679"/>
-    </row>
-    <row r="680" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT680"/>
-      <c r="CJ680" s="3"/>
-    </row>
-    <row r="681" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT681"/>
-      <c r="CJ681" s="3"/>
-    </row>
-    <row r="682" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT682"/>
-      <c r="CJ682" s="3"/>
-    </row>
-    <row r="683" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ683" s="3"/>
-    </row>
-    <row r="684" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT684"/>
-    </row>
-    <row r="685" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT685"/>
-      <c r="CJ685" s="3"/>
-    </row>
-    <row r="686" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS686" s="5"/>
-      <c r="BT686" s="6"/>
-      <c r="CJ686" s="3"/>
-    </row>
-    <row r="687" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CL662" s="5"/>
+    </row>
+    <row r="679" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV679"/>
+    </row>
+    <row r="680" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV680"/>
+      <c r="CL680" s="3"/>
+    </row>
+    <row r="681" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV681"/>
+      <c r="CL681" s="3"/>
+    </row>
+    <row r="682" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV682"/>
+      <c r="CL682" s="3"/>
+    </row>
+    <row r="683" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL683" s="3"/>
+    </row>
+    <row r="684" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV684"/>
+    </row>
+    <row r="685" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV685"/>
+      <c r="CL685" s="3"/>
+    </row>
+    <row r="686" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU686" s="5"/>
+      <c r="BV686" s="6"/>
+      <c r="CL686" s="3"/>
+    </row>
+    <row r="687" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H687" s="5"/>
-      <c r="CJ687" s="5"/>
-    </row>
-    <row r="690" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT690"/>
-    </row>
-    <row r="691" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT691"/>
-      <c r="CJ691" s="3"/>
-    </row>
-    <row r="692" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT692"/>
-      <c r="CJ692" s="3"/>
-    </row>
-    <row r="693" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT693"/>
-      <c r="CJ693" s="3"/>
-    </row>
-    <row r="694" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT694"/>
-      <c r="CJ694" s="3"/>
-    </row>
-    <row r="695" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT695"/>
-      <c r="CJ695" s="3"/>
-    </row>
-    <row r="696" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT696"/>
-      <c r="CJ696" s="3"/>
-    </row>
-    <row r="697" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT697"/>
-      <c r="CJ697" s="3"/>
-    </row>
-    <row r="698" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ698" s="3"/>
-    </row>
-    <row r="700" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT700"/>
-    </row>
-    <row r="701" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT701"/>
-      <c r="CJ701" s="3"/>
-    </row>
-    <row r="702" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT702"/>
-      <c r="CJ702" s="3"/>
-    </row>
-    <row r="703" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT703"/>
-      <c r="CJ703" s="3"/>
-    </row>
-    <row r="704" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT704"/>
-      <c r="CJ704" s="3"/>
-    </row>
-    <row r="705" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT705"/>
-      <c r="CJ705" s="3"/>
-    </row>
-    <row r="706" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ706" s="3"/>
-    </row>
-    <row r="707" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT707"/>
-    </row>
-    <row r="708" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT708"/>
-      <c r="CJ708" s="3"/>
-    </row>
-    <row r="709" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT709"/>
-      <c r="CJ709" s="3"/>
-    </row>
-    <row r="710" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT710"/>
-      <c r="CJ710" s="3"/>
-    </row>
-    <row r="711" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT711"/>
-      <c r="CJ711" s="3"/>
-    </row>
-    <row r="712" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT712"/>
-      <c r="CJ712" s="3"/>
-    </row>
-    <row r="713" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT713"/>
-      <c r="CJ713" s="3"/>
-    </row>
-    <row r="714" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT714"/>
-      <c r="CJ714" s="3"/>
-    </row>
-    <row r="715" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT715"/>
-      <c r="CJ715" s="3"/>
-    </row>
-    <row r="716" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT716"/>
-      <c r="CJ716" s="3"/>
-    </row>
-    <row r="717" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT717"/>
-      <c r="CJ717" s="3"/>
-    </row>
-    <row r="718" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT718"/>
-      <c r="CJ718" s="3"/>
-    </row>
-    <row r="719" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT719"/>
-      <c r="CJ719" s="3"/>
-    </row>
-    <row r="720" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT720"/>
-      <c r="CJ720" s="3"/>
-    </row>
-    <row r="721" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT721"/>
-      <c r="CJ721" s="3"/>
-    </row>
-    <row r="722" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT722"/>
-      <c r="CJ722" s="3"/>
-    </row>
-    <row r="723" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT723"/>
-      <c r="CJ723" s="3"/>
-    </row>
-    <row r="724" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT724"/>
-      <c r="CJ724" s="3"/>
-    </row>
-    <row r="725" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT725"/>
-      <c r="CJ725" s="3"/>
-    </row>
-    <row r="726" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT726"/>
-      <c r="CJ726" s="3"/>
-    </row>
-    <row r="727" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT727"/>
-      <c r="CJ727" s="3"/>
-    </row>
-    <row r="728" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT728"/>
-      <c r="CJ728" s="3"/>
-    </row>
-    <row r="729" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT729"/>
-      <c r="CJ729" s="3"/>
-    </row>
-    <row r="730" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT730"/>
-      <c r="CJ730" s="3"/>
-    </row>
-    <row r="731" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT731"/>
-      <c r="CJ731" s="3"/>
-    </row>
-    <row r="732" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT732"/>
-      <c r="CJ732" s="3"/>
-    </row>
-    <row r="733" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT733"/>
-      <c r="CJ733" s="3"/>
-    </row>
-    <row r="734" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT734"/>
-      <c r="CJ734" s="3"/>
-    </row>
-    <row r="735" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT735"/>
-      <c r="CJ735" s="3"/>
-    </row>
-    <row r="736" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT736"/>
-      <c r="CJ736" s="3"/>
-    </row>
-    <row r="737" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ737" s="3"/>
-    </row>
-    <row r="738" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT738"/>
-    </row>
-    <row r="739" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT739"/>
-      <c r="CJ739" s="3"/>
-    </row>
-    <row r="740" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT740"/>
-      <c r="CJ740" s="3"/>
-    </row>
-    <row r="741" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ741" s="3"/>
+      <c r="CL687" s="5"/>
+    </row>
+    <row r="690" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV690"/>
+    </row>
+    <row r="691" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV691"/>
+      <c r="CL691" s="3"/>
+    </row>
+    <row r="692" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV692"/>
+      <c r="CL692" s="3"/>
+    </row>
+    <row r="693" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV693"/>
+      <c r="CL693" s="3"/>
+    </row>
+    <row r="694" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV694"/>
+      <c r="CL694" s="3"/>
+    </row>
+    <row r="695" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV695"/>
+      <c r="CL695" s="3"/>
+    </row>
+    <row r="696" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV696"/>
+      <c r="CL696" s="3"/>
+    </row>
+    <row r="697" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV697"/>
+      <c r="CL697" s="3"/>
+    </row>
+    <row r="698" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL698" s="3"/>
+    </row>
+    <row r="700" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV700"/>
+    </row>
+    <row r="701" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV701"/>
+      <c r="CL701" s="3"/>
+    </row>
+    <row r="702" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV702"/>
+      <c r="CL702" s="3"/>
+    </row>
+    <row r="703" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV703"/>
+      <c r="CL703" s="3"/>
+    </row>
+    <row r="704" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV704"/>
+      <c r="CL704" s="3"/>
+    </row>
+    <row r="705" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV705"/>
+      <c r="CL705" s="3"/>
+    </row>
+    <row r="706" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL706" s="3"/>
+    </row>
+    <row r="707" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV707"/>
+    </row>
+    <row r="708" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV708"/>
+      <c r="CL708" s="3"/>
+    </row>
+    <row r="709" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV709"/>
+      <c r="CL709" s="3"/>
+    </row>
+    <row r="710" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV710"/>
+      <c r="CL710" s="3"/>
+    </row>
+    <row r="711" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV711"/>
+      <c r="CL711" s="3"/>
+    </row>
+    <row r="712" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV712"/>
+      <c r="CL712" s="3"/>
+    </row>
+    <row r="713" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV713"/>
+      <c r="CL713" s="3"/>
+    </row>
+    <row r="714" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV714"/>
+      <c r="CL714" s="3"/>
+    </row>
+    <row r="715" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV715"/>
+      <c r="CL715" s="3"/>
+    </row>
+    <row r="716" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV716"/>
+      <c r="CL716" s="3"/>
+    </row>
+    <row r="717" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV717"/>
+      <c r="CL717" s="3"/>
+    </row>
+    <row r="718" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV718"/>
+      <c r="CL718" s="3"/>
+    </row>
+    <row r="719" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV719"/>
+      <c r="CL719" s="3"/>
+    </row>
+    <row r="720" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV720"/>
+      <c r="CL720" s="3"/>
+    </row>
+    <row r="721" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV721"/>
+      <c r="CL721" s="3"/>
+    </row>
+    <row r="722" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV722"/>
+      <c r="CL722" s="3"/>
+    </row>
+    <row r="723" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV723"/>
+      <c r="CL723" s="3"/>
+    </row>
+    <row r="724" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV724"/>
+      <c r="CL724" s="3"/>
+    </row>
+    <row r="725" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV725"/>
+      <c r="CL725" s="3"/>
+    </row>
+    <row r="726" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV726"/>
+      <c r="CL726" s="3"/>
+    </row>
+    <row r="727" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV727"/>
+      <c r="CL727" s="3"/>
+    </row>
+    <row r="728" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV728"/>
+      <c r="CL728" s="3"/>
+    </row>
+    <row r="729" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV729"/>
+      <c r="CL729" s="3"/>
+    </row>
+    <row r="730" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV730"/>
+      <c r="CL730" s="3"/>
+    </row>
+    <row r="731" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV731"/>
+      <c r="CL731" s="3"/>
+    </row>
+    <row r="732" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV732"/>
+      <c r="CL732" s="3"/>
+    </row>
+    <row r="733" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV733"/>
+      <c r="CL733" s="3"/>
+    </row>
+    <row r="734" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV734"/>
+      <c r="CL734" s="3"/>
+    </row>
+    <row r="735" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV735"/>
+      <c r="CL735" s="3"/>
+    </row>
+    <row r="736" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV736"/>
+      <c r="CL736" s="3"/>
+    </row>
+    <row r="737" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL737" s="3"/>
+    </row>
+    <row r="738" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV738"/>
+    </row>
+    <row r="739" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV739"/>
+      <c r="CL739" s="3"/>
+    </row>
+    <row r="740" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV740"/>
+      <c r="CL740" s="3"/>
+    </row>
+    <row r="741" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL741" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
